--- a/data/trans_bre/IP16A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Clase-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 20,31</t>
+          <t>-28,31; 20,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 23,72</t>
+          <t>-33,95; 19,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 14,87</t>
+          <t>-28,98; 17,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 35,16</t>
+          <t>-37,93; 38,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 61,41</t>
+          <t>-52,38; 53,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 32,87</t>
+          <t>-43,6; 40,8</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 42,42</t>
+          <t>-10,68; 41,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 27,42</t>
+          <t>-30,24; 26,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 18,22</t>
+          <t>-31,67; 15,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 111,03</t>
+          <t>-13,61; 107,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,4; 56,76</t>
+          <t>-40,0; 49,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 31,06</t>
+          <t>-38,53; 29,13</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 29,54</t>
+          <t>-22,81; 29,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 50,29</t>
+          <t>-17,31; 51,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 38,62</t>
+          <t>-29,02; 38,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 51,02</t>
+          <t>-24,2; 51,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 157,58</t>
+          <t>-21,36; 169,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 125,17</t>
+          <t>-46,89; 117,22</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 16,01</t>
+          <t>-13,62; 16,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 34,05</t>
+          <t>-2,19; 31,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 36,31</t>
+          <t>-22,89; 36,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 33,54</t>
+          <t>-21,85; 34,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 105,2</t>
+          <t>-3,4; 91,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 79,85</t>
+          <t>-35,83; 78,92</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 18,64</t>
+          <t>-22,35; 19,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 15,59</t>
+          <t>-29,05; 14,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 18,3</t>
+          <t>-21,53; 20,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 32,15</t>
+          <t>-28,82; 33,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 26,79</t>
+          <t>-39,66; 27,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 38,99</t>
+          <t>-33,08; 43,7</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 43,67</t>
+          <t>-27,0; 42,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 58,98</t>
+          <t>-4,91; 60,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 28,86</t>
+          <t>-36,2; 28,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 100,6</t>
+          <t>-39,18; 101,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 342,92</t>
+          <t>-7,81; 319,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,1; 90,96</t>
+          <t>-58,35; 89,37</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 12,42</t>
+          <t>-6,48; 12,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 16,12</t>
+          <t>-4,43; 16,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 18,37</t>
+          <t>-11,78; 18,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 21,14</t>
+          <t>-9,82; 21,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 33,97</t>
+          <t>-7,23; 33,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 35,73</t>
+          <t>-19,36; 35,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Clase-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 20,91</t>
+          <t>-28,44; 19,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 19,63</t>
+          <t>-34,85; 22,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 17,42</t>
+          <t>-29,77; 15,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 38,24</t>
+          <t>-36,57; 33,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 53,62</t>
+          <t>-54,36; 57,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 40,8</t>
+          <t>-44,09; 33,68</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 41,09</t>
+          <t>-10,42; 40,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 26,23</t>
+          <t>-31,15; 24,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 15,92</t>
+          <t>-28,2; 18,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 107,79</t>
+          <t>-12,81; 108,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,0; 49,39</t>
+          <t>-42,41; 45,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 29,13</t>
+          <t>-35,32; 32,13</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 29,29</t>
+          <t>-22,69; 29,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 51,54</t>
+          <t>-18,35; 50,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 38,75</t>
+          <t>-27,63; 37,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 51,76</t>
+          <t>-24,25; 53,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 169,6</t>
+          <t>-25,91; 164,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,89; 117,22</t>
+          <t>-46,61; 115,97</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 16,6</t>
+          <t>-14,48; 17,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 31,07</t>
+          <t>-2,6; 32,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 36,6</t>
+          <t>-24,81; 35,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 34,18</t>
+          <t>-23,4; 37,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 91,22</t>
+          <t>-4,55; 101,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 78,92</t>
+          <t>-38,04; 72,66</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 19,99</t>
+          <t>-20,86; 21,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 14,87</t>
+          <t>-32,26; 13,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 20,1</t>
+          <t>-23,75; 18,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 33,9</t>
+          <t>-27,65; 41,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 27,11</t>
+          <t>-41,93; 23,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 43,7</t>
+          <t>-35,22; 38,14</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 42,54</t>
+          <t>-29,87; 44,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 60,56</t>
+          <t>-6,85; 60,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 28,73</t>
+          <t>-37,66; 28,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 101,51</t>
+          <t>-40,45; 106,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 319,18</t>
+          <t>-12,28; 313,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 89,37</t>
+          <t>-60,91; 92,47</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 12,63</t>
+          <t>-5,97; 12,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 16,56</t>
+          <t>-4,16; 16,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 18,72</t>
+          <t>-12,54; 19,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 21,43</t>
+          <t>-8,96; 21,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 33,09</t>
+          <t>-6,96; 36,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 35,97</t>
+          <t>-20,29; 37,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,67</t>
+          <t>-4,52</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-11,77%</t>
+          <t>-8,16%</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 19,54</t>
+          <t>-28,08; 20,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 22,46</t>
+          <t>-33,67; 23,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 15,22</t>
+          <t>-26,21; 18,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 33,6</t>
+          <t>-36,24; 35,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-54,36; 57,06</t>
+          <t>-55,86; 61,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 33,68</t>
+          <t>-39,16; 40,58</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,92</t>
+          <t>-7,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-8,44%</t>
+          <t>-10,06%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 40,29</t>
+          <t>-12,55; 42,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 24,37</t>
+          <t>-31,6; 27,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 18,07</t>
+          <t>-28,63; 17,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 108,53</t>
+          <t>-15,1; 111,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 45,62</t>
+          <t>-41,4; 56,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 32,13</t>
+          <t>-37,2; 31,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>-2,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>-5,31%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 29,0</t>
+          <t>-19,72; 29,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 50,84</t>
+          <t>-19,94; 50,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 37,88</t>
+          <t>-36,45; 32,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 53,1</t>
+          <t>-22,81; 51,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 164,5</t>
+          <t>-27,17; 157,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 115,97</t>
+          <t>-55,15; 92,11</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>-6,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>-9,8%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 17,45</t>
+          <t>-15,86; 16,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 32,75</t>
+          <t>-3,01; 34,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 35,59</t>
+          <t>-23,99; 17,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 37,82</t>
+          <t>-24,29; 33,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 101,59</t>
+          <t>-4,94; 105,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,04; 72,66</t>
+          <t>-33,82; 32,95</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-2,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,0%</t>
+          <t>-4,98%</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 21,73</t>
+          <t>-20,81; 18,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 13,19</t>
+          <t>-29,81; 15,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 18,82</t>
+          <t>-23,9; 16,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 41,44</t>
+          <t>-27,44; 32,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 23,04</t>
+          <t>-39,73; 26,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 38,14</t>
+          <t>-35,56; 34,22</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-4,7</t>
+          <t>-4,4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-9,58%</t>
+          <t>-9,11%</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 44,34</t>
+          <t>-34,13; 43,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 60,84</t>
+          <t>-6,22; 58,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 28,12</t>
+          <t>-33,21; 28,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 106,3</t>
+          <t>-49,3; 100,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 313,37</t>
+          <t>-10,65; 342,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,91; 92,47</t>
+          <t>-56,09; 92,58</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-0,05%</t>
+          <t>-7,66%</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 12,52</t>
+          <t>-5,54; 12,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 16,77</t>
+          <t>-4,97; 16,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 19,7</t>
+          <t>-14,34; 5,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 21,58</t>
+          <t>-8,17; 21,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 36,03</t>
+          <t>-8,25; 33,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 37,38</t>
+          <t>-22,76; 9,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,88</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-5,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-12,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-8,16%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-7.463666503631525</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.878797776255164</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6086409343560015</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.922035071571413</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.3392237687060751</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1106093572177477</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.06489156291195811</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.07031249312797612</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-28,08; 20,31</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-33,67; 23,72</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-26,21; 18,15</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-36,24; 35,16</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-55,86; 61,41</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-39,16; 40,58</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-15.83198110725563</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-11.07217094773088</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.47579406483791</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.035797261191407</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5937884996974059</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5125104161135133</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5898489107795339</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4940973243132025</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9161757584657817</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.09275178937661</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.123264755792716</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.744626590437072</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.08062609276261808</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.6712081996998347</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.286837806920525</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.7568206138983254</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14,53</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-7,07</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,57%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-10,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-12,55; 42,42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-31,6; 27,42</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-28,63; 17,95</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-15,1; 111,03</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-41,4; 56,76</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-37,2; 31,49</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.462273135950654</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>10.89660981538715</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-3.745154372692151</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.356064259803234</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.0703976679291279</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.43660219732681</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.3393554294168419</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1354274358144463</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,96</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,78</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-5,31%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.639202386420115</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3.388830023718518</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.75856235245452</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-12.15154284948283</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3525999054228164</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.2024968443800924</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6862557330127927</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5386649676421875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-19,72; 29,54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-19,94; 50,29</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-36,45; 32,27</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-22,81; 51,02</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-27,17; 157,58</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-55,15; 92,11</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11.00941876899073</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>18.68404684957</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.655728638455366</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6.09723258169617</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7351519136961761</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3.799385218098743</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4232632166345976</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4990908261849224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,36</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-6,07</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-9,8%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.614426363093291</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1473094831931768</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.150105286130615</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-4.994754106269589</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2540495564699844</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.0133004209493693</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4317354159148079</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.3613548966452458</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-15,86; 16,01</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 34,05</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-23,99; 17,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-24,29; 33,54</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-4,94; 105,2</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-33,82; 32,95</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.63381957343867</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.955093009901424</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.040865556960003</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-15.26575177122901</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5891189128192373</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5324823556385898</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4797018200296897</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7502668875449325</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.030824408081885</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.325636936040339</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.40841731571425</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.806397012196721</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2573836150125414</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.051497468923787</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3.445665093658757</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5175289392511119</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-8,3</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,92</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-12,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-4,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-20,81; 18,64</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-29,81; 15,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-23,9; 16,58</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-27,44; 32,15</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-39,73; 26,79</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-35,56; 34,22</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.4217025675950309</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.225376512168055</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5.189216437547062</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.964637629282751</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02196876026240839</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.08413985879252878</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.701980213321564</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1288044193313811</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11,07</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29,6</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,4</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-9,11%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.046947607519138</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.262090453716295</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7723258833544469</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.109348684886703</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3130082887627834</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3738698020104683</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.04893386580585823</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4530393802381907</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-34,13; 43,67</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-6,22; 58,98</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-33,21; 28,64</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-49,3; 100,6</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-10,65; 342,92</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-56,09; 92,58</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.554773641176984</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.655071153210257</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.01458231385964</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.44709144580768</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.332353574293243</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.4145965538872671</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.968443164079966</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3482543676076686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,79</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-7,66%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.6679055292849623</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5597789259318836</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.5496918287370047</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.8019551890677351</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.03557364200209631</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.04142911191804756</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.0461021857514114</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.06301026539864077</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-5,54; 12,42</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-4,97; 16,12</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-14,34; 5,34</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-8,17; 21,14</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-8,25; 33,97</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-22,76; 9,77</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-9.222756991190098</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.079496287074893</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.975231800586602</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.309677896923449</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4133078965536067</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4498191145737849</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4720517272588177</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3857231737952286</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.683779780018174</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.609034296500693</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.547207776420779</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.51129258646259</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5423239462276509</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.5651047190033501</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6631078109631553</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.7762130851214953</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-5.6644504900052</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.942033263260773</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>9.071230120944323</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-2.216306843363393</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3617090626287091</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1746335452655127</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>1.57469293356578</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.2218834894246396</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-14.38026893558907</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-9.52051658968748</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>1.095538563212237</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-10.40931820886281</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.7023771262674583</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6486181250804391</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.01391505764435902</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.720878631889222</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.172088189187743</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>7.349786836571824</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>19.34257941219703</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>5.975294494519997</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.3762946274610061</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.124467819169535</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>6.277455309011266</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>1.325588421756204</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-2.586205978933847</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.6217069268410313</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2.042288053371587</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.560650624410929</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1308624922871647</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.04805728531288447</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.226973974040284</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.111675646345553</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-5.83342926572748</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.447926585934639</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.5106196712365866</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.610233593869832</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.264741232308785</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1665657400173184</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.04998232572542635</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3028676314183498</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.747378612761772</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.370502874306676</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.576779931352116</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.453859954512451</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.041519839910484</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.2939789027736124</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.623465366536671</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.1158517839527211</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
